--- a/docs/Decodifiche/155_dmnm_dec_livello_istruzione.xlsx
+++ b/docs/Decodifiche/155_dmnm_dec_livello_istruzione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>(Laurea)</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:16.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>(Licenza elementare o nessun titolo)</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:17.0</t>
   </si>
 </sst>
 </file>
@@ -227,7 +224,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
